--- a/Module-3-DataScientist and ML/results/reports/02_feature_engineering_report.xlsx
+++ b/Module-3-DataScientist and ML/results/reports/02_feature_engineering_report.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -686,7 +686,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Risk indicator for low priority trades</t>
+          <t>Risk indicator for low settle priority</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,131 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>party_priority_risk</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Risk indicator for low party priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Risk Features</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>combined_priority_risk</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Both priorities are LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Risk Features</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>is_complex_trade</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Indicator for complex/risky trade combinations</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Risk Features</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>is_high_risk_combo</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>OTC + non-major + low priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Risk Features</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>msg_fctn_risk</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Message function is not PREADVICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Risk Features</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>weekend_settlement_risk</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Settlement on weekend</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Risk Features</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>is_urgent_settlement</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Settlement within 1 day</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Risk Features</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>is_delayed_settlement</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Settlement after 5+ days</t>
         </is>
       </c>
     </row>
@@ -718,7 +837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1021,25 +1140,25 @@
         <v>2000</v>
       </c>
       <c r="C10" t="n">
-        <v>2.6125</v>
+        <v>2.0325</v>
       </c>
       <c r="D10" t="n">
-        <v>1.143677292278918</v>
+        <v>0.7400794611421143</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
         <v>3</v>
       </c>
-      <c r="H10" t="n">
-        <v>4</v>
-      </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1107,17 +1226,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>is_complex_trade</t>
+          <t>party_priority_risk</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2000</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1705</v>
+        <v>0.432</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3761655224101819</v>
+        <v>0.4954783036366854</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1129,10 +1248,227 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>combined_priority_risk</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.4656201789823308</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>is_complex_trade</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.06950000000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.254366076846983</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>is_high_risk_combo</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.1467200169768626</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>msg_fctn_risk</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>weekend_settlement_risk</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.4339837796052754</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>is_urgent_settlement</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5835</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.4931017386527157</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>is_delayed_settlement</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1146,7 +1482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P101"/>
+  <dimension ref="A1:W101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1227,7 +1563,42 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>party_priority_risk</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>combined_priority_risk</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
           <t>is_complex_trade</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>is_high_risk_combo</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>msg_fctn_risk</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>weekend_settlement_risk</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>is_urgent_settlement</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>is_delayed_settlement</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1639,11 @@
           <t>USD_OTCO</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -1284,6 +1659,27 @@
         <v>1</v>
       </c>
       <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1324,7 +1720,11 @@
           <t>INR_EXCH</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -1340,6 +1740,27 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1380,7 +1801,11 @@
           <t>GBP_EXCH</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -1396,6 +1821,27 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1436,7 +1882,11 @@
           <t>INR_SECM</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>PREADVICE_SECM</t>
@@ -1452,6 +1902,27 @@
         <v>1</v>
       </c>
       <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1492,7 +1963,11 @@
           <t>INR_SECM</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>PREADVICE_SECM</t>
@@ -1508,6 +1983,27 @@
         <v>1</v>
       </c>
       <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1548,7 +2044,11 @@
           <t>USD_EXCH</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -1564,6 +2064,27 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1604,7 +2125,11 @@
           <t>USD_OTCO</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -1622,6 +2147,27 @@
       <c r="P8" t="n">
         <v>0</v>
       </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1660,14 +2206,18 @@
           <t>INR_PRIM</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>PREADVICE_PRIM</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1676,7 +2226,28 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1716,7 +2287,11 @@
           <t>USD_SECM</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>PREADVICE_SECM</t>
@@ -1732,6 +2307,27 @@
         <v>1</v>
       </c>
       <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1772,7 +2368,11 @@
           <t>INR_EXCH</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -1788,6 +2388,27 @@
         <v>1</v>
       </c>
       <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1828,7 +2449,11 @@
           <t>GBP_EXCH</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -1844,6 +2469,27 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1884,7 +2530,11 @@
           <t>USD_OTCO</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -1900,6 +2550,27 @@
         <v>1</v>
       </c>
       <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1940,14 +2611,18 @@
           <t>GBP_PRIM</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>PREADVICE_PRIM</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
@@ -1956,6 +2631,27 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1996,7 +2692,11 @@
           <t>USD_SECM</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>PREADVICE_SECM</t>
@@ -2012,6 +2712,27 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2052,7 +2773,11 @@
           <t>GBP_SECM</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>PREADVICE_SECM</t>
@@ -2068,6 +2793,27 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2108,14 +2854,18 @@
           <t>USD_PRIM</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>PREADVICE_PRIM</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
@@ -2124,6 +2874,27 @@
         <v>1</v>
       </c>
       <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2164,14 +2935,18 @@
           <t>USD_PRIM</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>PREADVICE_PRIM</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N18" t="n">
         <v>1</v>
@@ -2180,6 +2955,27 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2220,7 +3016,11 @@
           <t>USD_OTCO</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -2238,6 +3038,27 @@
       <c r="P19" t="n">
         <v>0</v>
       </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2276,14 +3097,18 @@
           <t>INR_PRIM</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>PREADVICE_PRIM</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2292,7 +3117,28 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2332,7 +3178,11 @@
           <t>GBP_OTCO</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -2348,6 +3198,27 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2388,7 +3259,11 @@
           <t>USD_EXCH</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -2404,6 +3279,27 @@
         <v>1</v>
       </c>
       <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2444,7 +3340,11 @@
           <t>USD_EXCH</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -2460,6 +3360,27 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2500,14 +3421,18 @@
           <t>GBP_PRIM</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>PREADVICE_PRIM</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N24" t="n">
         <v>1</v>
@@ -2516,6 +3441,27 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2556,7 +3502,11 @@
           <t>USD_EXCH</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -2572,6 +3522,27 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2612,7 +3583,11 @@
           <t>INR_OTCO</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -2628,7 +3603,28 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2668,7 +3664,11 @@
           <t>GBP_EXCH</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -2684,6 +3684,27 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2724,14 +3745,18 @@
           <t>USD_PRIM</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>PREADVICE_PRIM</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N28" t="n">
         <v>1</v>
@@ -2740,6 +3765,27 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2780,7 +3826,11 @@
           <t>GBP_EXCH</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -2796,6 +3846,27 @@
         <v>1</v>
       </c>
       <c r="P29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2836,7 +3907,11 @@
           <t>USD_OTCO</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -2854,6 +3929,27 @@
       <c r="P30" t="n">
         <v>0</v>
       </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2892,7 +3988,11 @@
           <t>USD_EXCH</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -2908,6 +4008,27 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2948,7 +4069,11 @@
           <t>USD_OTCO</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -2966,6 +4091,27 @@
       <c r="P32" t="n">
         <v>0</v>
       </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3004,7 +4150,11 @@
           <t>USD_EXCH</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -3020,6 +4170,27 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3060,14 +4231,18 @@
           <t>INR_PRIM</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>PREADVICE_PRIM</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -3076,7 +4251,28 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -3116,7 +4312,11 @@
           <t>GBP_SECM</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>PREADVICE_SECM</t>
@@ -3132,6 +4332,27 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3172,7 +4393,11 @@
           <t>GBP_OTCO</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -3188,6 +4413,27 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3228,7 +4474,11 @@
           <t>INR_OTCO</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -3246,6 +4496,27 @@
       <c r="P37" t="n">
         <v>1</v>
       </c>
+      <c r="Q37" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3284,14 +4555,18 @@
           <t>GBP_PRIM</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>PREADVICE_PRIM</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N38" t="n">
         <v>1</v>
@@ -3300,6 +4575,27 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3340,7 +4636,11 @@
           <t>USD_EXCH</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -3356,6 +4656,27 @@
         <v>1</v>
       </c>
       <c r="P39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3396,7 +4717,11 @@
           <t>INR_EXCH</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -3412,6 +4737,27 @@
         <v>1</v>
       </c>
       <c r="P40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3452,7 +4798,11 @@
           <t>GBP_EXCH</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -3468,6 +4818,27 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3508,7 +4879,11 @@
           <t>USD_EXCH</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -3524,6 +4899,27 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3564,7 +4960,11 @@
           <t>USD_EXCH</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -3580,6 +4980,27 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3620,7 +5041,11 @@
           <t>USD_OTCO</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -3636,6 +5061,27 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3676,7 +5122,11 @@
           <t>GBP_OTCO</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -3692,6 +5142,27 @@
         <v>1</v>
       </c>
       <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3732,7 +5203,11 @@
           <t>INR_OTCO</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -3749,6 +5224,27 @@
       </c>
       <c r="P46" t="n">
         <v>1</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3788,7 +5284,11 @@
           <t>GBP_SECM</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>PREADVICE_SECM</t>
@@ -3804,6 +5304,27 @@
         <v>1</v>
       </c>
       <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3844,7 +5365,11 @@
           <t>INR_SECM</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>PREADVICE_SECM</t>
@@ -3860,6 +5385,27 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3900,7 +5446,11 @@
           <t>USD_SECM</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>PREADVICE_SECM</t>
@@ -3916,6 +5466,27 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3956,7 +5527,11 @@
           <t>GBP_OTCO</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -3972,6 +5547,27 @@
         <v>1</v>
       </c>
       <c r="P50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4012,14 +5608,18 @@
           <t>INR_PRIM</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>PREADVICE_PRIM</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
@@ -4028,7 +5628,28 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -4068,7 +5689,11 @@
           <t>INR_OTCO</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -4085,6 +5710,27 @@
       </c>
       <c r="P52" t="n">
         <v>1</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1</v>
+      </c>
+      <c r="S52" t="n">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -4124,7 +5770,11 @@
           <t>USD_SECM</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>PREADVICE_SECM</t>
@@ -4140,6 +5790,27 @@
         <v>1</v>
       </c>
       <c r="P53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4180,7 +5851,11 @@
           <t>INR_OTCO</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -4196,7 +5871,28 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -4236,7 +5932,11 @@
           <t>INR_EXCH</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -4252,6 +5952,27 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4292,7 +6013,11 @@
           <t>USD_SECM</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>PREADVICE_SECM</t>
@@ -4308,6 +6033,27 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4348,7 +6094,11 @@
           <t>GBP_OTCO</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -4366,6 +6116,27 @@
       <c r="P57" t="n">
         <v>0</v>
       </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4404,14 +6175,18 @@
           <t>USD_PRIM</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>PREADVICE_PRIM</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N58" t="n">
         <v>1</v>
@@ -4420,6 +6195,27 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1</v>
+      </c>
+      <c r="W58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4460,14 +6256,18 @@
           <t>USD_PRIM</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>PREADVICE_PRIM</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N59" t="n">
         <v>1</v>
@@ -4476,6 +6276,27 @@
         <v>1</v>
       </c>
       <c r="P59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4516,7 +6337,11 @@
           <t>USD_SECM</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>PREADVICE_SECM</t>
@@ -4532,6 +6357,27 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4572,7 +6418,11 @@
           <t>INR_OTCO</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -4588,7 +6438,28 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -4628,7 +6499,11 @@
           <t>USD_SECM</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>PREADVICE_SECM</t>
@@ -4644,6 +6519,27 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4684,7 +6580,11 @@
           <t>GBP_EXCH</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -4700,6 +6600,27 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4740,7 +6661,11 @@
           <t>GBP_OTCO</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -4756,6 +6681,27 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4796,7 +6742,11 @@
           <t>USD_SECM</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>PREADVICE_SECM</t>
@@ -4812,6 +6762,27 @@
         <v>1</v>
       </c>
       <c r="P65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4852,7 +6823,11 @@
           <t>INR_EXCH</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -4868,6 +6843,27 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4908,7 +6904,11 @@
           <t>INR_SECM</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>PREADVICE_SECM</t>
@@ -4924,6 +6924,27 @@
         <v>1</v>
       </c>
       <c r="P67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4964,7 +6985,11 @@
           <t>GBP_EXCH</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -4980,6 +7005,27 @@
         <v>0</v>
       </c>
       <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5020,7 +7066,11 @@
           <t>USD_EXCH</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -5036,6 +7086,27 @@
         <v>1</v>
       </c>
       <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>1</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5076,14 +7147,18 @@
           <t>USD_PRIM</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>PREADVICE_PRIM</t>
         </is>
       </c>
       <c r="M70" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N70" t="n">
         <v>1</v>
@@ -5092,6 +7167,27 @@
         <v>1</v>
       </c>
       <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>1</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5132,7 +7228,11 @@
           <t>GBP_SECM</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>PREADVICE_SECM</t>
@@ -5148,6 +7248,27 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5188,7 +7309,11 @@
           <t>INR_OTCO</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -5204,7 +7329,28 @@
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -5244,7 +7390,11 @@
           <t>USD_EXCH</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -5260,6 +7410,27 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1</v>
+      </c>
+      <c r="W73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5300,14 +7471,18 @@
           <t>USD_PRIM</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>PREADVICE_PRIM</t>
         </is>
       </c>
       <c r="M74" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N74" t="n">
         <v>1</v>
@@ -5316,6 +7491,27 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5356,7 +7552,11 @@
           <t>GBP_EXCH</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -5372,6 +7572,27 @@
         <v>1</v>
       </c>
       <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5412,7 +7633,11 @@
           <t>INR_EXCH</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -5428,6 +7653,27 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" t="n">
+        <v>1</v>
+      </c>
+      <c r="W76" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5468,7 +7714,11 @@
           <t>USD_SECM</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>PREADVICE_SECM</t>
@@ -5484,6 +7734,27 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5524,7 +7795,11 @@
           <t>USD_OTCO</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -5540,6 +7815,27 @@
         <v>1</v>
       </c>
       <c r="P78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
+      </c>
+      <c r="V78" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5580,7 +7876,11 @@
           <t>INR_EXCH</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -5596,6 +7896,27 @@
         <v>1</v>
       </c>
       <c r="P79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>1</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5636,7 +7957,11 @@
           <t>USD_OTCO</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -5652,6 +7977,27 @@
         <v>1</v>
       </c>
       <c r="P80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>1</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
+      </c>
+      <c r="V80" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5692,14 +8038,18 @@
           <t>USD_PRIM</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>PREADVICE_PRIM</t>
         </is>
       </c>
       <c r="M81" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N81" t="n">
         <v>1</v>
@@ -5708,6 +8058,27 @@
         <v>1</v>
       </c>
       <c r="P81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>1</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5748,7 +8119,11 @@
           <t>INR_OTCO</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -5764,7 +8139,28 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>1</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" t="n">
+        <v>1</v>
+      </c>
+      <c r="W82" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -5804,7 +8200,11 @@
           <t>USD_SECM</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>PREADVICE_SECM</t>
@@ -5820,6 +8220,27 @@
         <v>1</v>
       </c>
       <c r="P83" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>1</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="n">
+        <v>1</v>
+      </c>
+      <c r="V83" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5860,7 +8281,11 @@
           <t>GBP_EXCH</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -5876,6 +8301,27 @@
         <v>0</v>
       </c>
       <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0</v>
+      </c>
+      <c r="V84" t="n">
+        <v>1</v>
+      </c>
+      <c r="W84" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5916,14 +8362,18 @@
           <t>GBP_PRIM</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>PREADVICE_PRIM</t>
         </is>
       </c>
       <c r="M85" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N85" t="n">
         <v>1</v>
@@ -5932,6 +8382,27 @@
         <v>0</v>
       </c>
       <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" t="n">
+        <v>1</v>
+      </c>
+      <c r="W85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5972,7 +8443,11 @@
           <t>USD_SECM</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>PREADVICE_SECM</t>
@@ -5988,6 +8463,27 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" t="n">
+        <v>1</v>
+      </c>
+      <c r="W86" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6028,7 +8524,11 @@
           <t>USD_OTCO</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -6044,6 +8544,27 @@
         <v>1</v>
       </c>
       <c r="P87" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>1</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" t="n">
+        <v>0</v>
+      </c>
+      <c r="U87" t="n">
+        <v>1</v>
+      </c>
+      <c r="V87" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6084,14 +8605,18 @@
           <t>INR_PRIM</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>PREADVICE_PRIM</t>
         </is>
       </c>
       <c r="M88" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N88" t="n">
         <v>0</v>
@@ -6100,7 +8625,28 @@
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" t="n">
+        <v>1</v>
+      </c>
+      <c r="W88" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -6140,7 +8686,11 @@
           <t>USD_OTCO</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -6156,6 +8706,27 @@
         <v>1</v>
       </c>
       <c r="P89" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>1</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="n">
+        <v>1</v>
+      </c>
+      <c r="V89" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6196,7 +8767,11 @@
           <t>USD_EXCH</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -6212,6 +8787,27 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" t="n">
+        <v>1</v>
+      </c>
+      <c r="W90" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6252,7 +8848,11 @@
           <t>INR_OTCO</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -6268,7 +8868,28 @@
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>1</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" t="n">
+        <v>0</v>
+      </c>
+      <c r="W91" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -6308,7 +8929,11 @@
           <t>INR_SECM</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>PREADVICE_SECM</t>
@@ -6324,6 +8949,27 @@
         <v>1</v>
       </c>
       <c r="P92" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>1</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" t="n">
+        <v>1</v>
+      </c>
+      <c r="V92" t="n">
+        <v>0</v>
+      </c>
+      <c r="W92" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6364,7 +9010,11 @@
           <t>USD_OTCO</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -6382,6 +9032,27 @@
       <c r="P93" t="n">
         <v>0</v>
       </c>
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6420,7 +9091,11 @@
           <t>USD_SECM</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>PREADVICE_SECM</t>
@@ -6436,6 +9111,27 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" t="n">
+        <v>0</v>
+      </c>
+      <c r="V94" t="n">
+        <v>1</v>
+      </c>
+      <c r="W94" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6476,7 +9172,11 @@
           <t>GBP_OTCO</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>PREADVICE_OTCO</t>
@@ -6494,6 +9194,27 @@
       <c r="P95" t="n">
         <v>0</v>
       </c>
+      <c r="Q95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" t="n">
+        <v>1</v>
+      </c>
+      <c r="W95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6532,7 +9253,11 @@
           <t>USD_EXCH</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -6548,6 +9273,27 @@
         <v>0</v>
       </c>
       <c r="P96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6588,7 +9334,11 @@
           <t>INR_EXCH</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>PREADVICE_EXCH</t>
@@ -6604,6 +9354,27 @@
         <v>0</v>
       </c>
       <c r="P97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" t="n">
+        <v>0</v>
+      </c>
+      <c r="V97" t="n">
+        <v>0</v>
+      </c>
+      <c r="W97" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6644,14 +9415,18 @@
           <t>INR_PRIM</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>MEDIUM_MEDIUM</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>PREADVICE_PRIM</t>
         </is>
       </c>
       <c r="M98" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N98" t="n">
         <v>0</v>
@@ -6660,7 +9435,28 @@
         <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" t="n">
+        <v>0</v>
+      </c>
+      <c r="V98" t="n">
+        <v>0</v>
+      </c>
+      <c r="W98" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -6700,7 +9496,11 @@
           <t>INR_SECM</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>LOW_LOW</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>PREADVICE_SECM</t>
@@ -6716,6 +9516,27 @@
         <v>1</v>
       </c>
       <c r="P99" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>1</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="n">
+        <v>0</v>
+      </c>
+      <c r="T99" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" t="n">
+        <v>1</v>
+      </c>
+      <c r="V99" t="n">
+        <v>0</v>
+      </c>
+      <c r="W99" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6756,7 +9577,11 @@
           <t>GBP_SECM</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>PREADVICE_SECM</t>
@@ -6772,6 +9597,27 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="n">
+        <v>0</v>
+      </c>
+      <c r="T100" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" t="n">
+        <v>0</v>
+      </c>
+      <c r="V100" t="n">
+        <v>1</v>
+      </c>
+      <c r="W100" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6812,7 +9658,11 @@
           <t>USD_SECM</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>HIGH_HIGH</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>PREADVICE_SECM</t>
@@ -6828,6 +9678,27 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="n">
+        <v>0</v>
+      </c>
+      <c r="T101" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" t="n">
+        <v>1</v>
+      </c>
+      <c r="W101" t="n">
         <v>0</v>
       </c>
     </row>
